--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hinam\OneDrive\Documents\CHWEETS\013_大正よいどれ\006.LINEアプリ\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684F9D34-F25C-4BCD-A797-E35C8ED2DDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FD13D4-A2A0-4400-96BB-2889C1E5178B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -530,7 +530,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>tようび.jpg</t>
+    <t>001.jpg</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -631,7 +631,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>

--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -5,23 +5,40 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hinam\OneDrive\Documents\CHWEETS\013_大正よいどれ\006.LINEアプリ\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C10844D-7DDF-42F5-AB81-47D593BD005A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1235884-C1F9-4C56-AF5A-0B9EFD68F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="店舗一覧" sheetId="1" r:id="rId1"/>
     <sheet name="イベント期間" sheetId="2" r:id="rId2"/>
+    <sheet name="店舗一覧 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">店舗一覧!$A$1:$X$34</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="386">
   <si>
     <t>ID</t>
   </si>
@@ -559,13 +576,1039 @@
       <t>コミ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>他クーポン併用不可。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バーガー酒場ハンバーガー・ママ</t>
+    <rPh sb="4" eb="6">
+      <t>サカバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一品と酒とグルメバーガー</t>
+  </si>
+  <si>
+    <t>大正焼肉SUNナスビ!!</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヤキニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通える高級焼肉</t>
+  </si>
+  <si>
+    <t>大正居酒屋タイガーパンチ</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>イザカヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>創作ガチ中華</t>
+  </si>
+  <si>
+    <t>ハイエナハイツ</t>
+  </si>
+  <si>
+    <t>ジビエ・肉料理</t>
+  </si>
+  <si>
+    <t>CHWEETS</t>
+  </si>
+  <si>
+    <t>クレープ酒場・夜カフェ</t>
+    <rPh sb="4" eb="6">
+      <t>サカバ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BAR K'S〜ケーズ〜</t>
+  </si>
+  <si>
+    <t>ダーツ・カラオケ</t>
+  </si>
+  <si>
+    <t>Bar Six Nine</t>
+  </si>
+  <si>
+    <t>ショットバー</t>
+  </si>
+  <si>
+    <t>だしと鶏ちゃぼ大正店</t>
+    <rPh sb="3" eb="4">
+      <t>トリ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>タイショウミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼き鳥・お出汁料理</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>トリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ダシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ふじわら君</t>
+  </si>
+  <si>
+    <t>創作料理居酒屋</t>
+    <rPh sb="4" eb="7">
+      <t>イザカヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大正サロン髭とボヰン</t>
+  </si>
+  <si>
+    <t>立ち飲み・創作料理　</t>
+  </si>
+  <si>
+    <t>大正バル誠~ｓｅｉ~</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>串カツ・牡蠣・沖縄料理</t>
+    <rPh sb="0" eb="1">
+      <t>クシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>居酒屋たすいち</t>
+    <rPh sb="0" eb="3">
+      <t>イザカヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もつ鍋酒屋</t>
+    <rPh sb="2" eb="3">
+      <t>ナベ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サカヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地鶏る</t>
+  </si>
+  <si>
+    <t>宮崎鶏の炭火焼き</t>
+  </si>
+  <si>
+    <t>沖縄酒場きじむなーの森</t>
+  </si>
+  <si>
+    <t>沖縄料理</t>
+    <rPh sb="2" eb="4">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナンチャツ亭のエリー</t>
+  </si>
+  <si>
+    <t>昭和レトロなおばんざい</t>
+  </si>
+  <si>
+    <t>Neboke-ネボケ</t>
+  </si>
+  <si>
+    <t>隠れ家バー</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>串焼き酒場ニコヤ</t>
+  </si>
+  <si>
+    <t>創作鉄板串焼き</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テッパン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クシヤキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Barカセット</t>
+  </si>
+  <si>
+    <t>80's・ロック・駄菓子</t>
+    <rPh sb="9" eb="12">
+      <t>ダガシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼肉ホルモンたろちゃん大正橋店</t>
+    <rPh sb="0" eb="2">
+      <t>ヤキニク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>タイショウバシ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>駅前で昼から飲める店</t>
+    <rPh sb="0" eb="2">
+      <t>エキマエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒル</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鉄板焼き栄八大阪大正店</t>
+    <rPh sb="0" eb="3">
+      <t>テッパンヤ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オオサカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お好み・焼きそば・鉄板居酒屋</t>
+  </si>
+  <si>
+    <t>うて食堂 大正BASE</t>
+  </si>
+  <si>
+    <t>蒸し料理で飲める食堂</t>
+  </si>
+  <si>
+    <t>大正焼肉ホルモンK2+</t>
+  </si>
+  <si>
+    <t>焼肉ホルモン・韓国料理</t>
+    <rPh sb="7" eb="9">
+      <t>カンコク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呑み処　三日月</t>
+  </si>
+  <si>
+    <t>カラオケ居酒屋</t>
+    <rPh sb="4" eb="7">
+      <t>イザカヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呑笑戎屋</t>
+  </si>
+  <si>
+    <t>地元親子の大衆居酒屋</t>
+  </si>
+  <si>
+    <t>三ちゃん</t>
+    <rPh sb="0" eb="1">
+      <t>サン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>海鮮居酒屋</t>
+  </si>
+  <si>
+    <t>SoundBar花いち</t>
+    <rPh sb="8" eb="9">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カラオケバー</t>
+  </si>
+  <si>
+    <t>ザ·沖縄</t>
+  </si>
+  <si>
+    <t>沖縄料理・カラオケ居酒屋</t>
+    <rPh sb="0" eb="4">
+      <t>オキナワリョウリ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>イザカヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚と沖縄料理 えっせんす</t>
+  </si>
+  <si>
+    <t>お酒は地球を救う</t>
+    <rPh sb="1" eb="2">
+      <t>サケ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チキュウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bar Coco-Color</t>
+  </si>
+  <si>
+    <t>カジュアルバー</t>
+  </si>
+  <si>
+    <t>福人(ふくんちゅ)</t>
+  </si>
+  <si>
+    <t>作りたいもん作りまっせ居酒屋</t>
+  </si>
+  <si>
+    <t>TM's DINER</t>
+  </si>
+  <si>
+    <t>イタリアン・メキシカン・アメリカン</t>
+  </si>
+  <si>
+    <t>Pizzeria Legare</t>
+  </si>
+  <si>
+    <t>本格ピッツァ・ドイツワイン</t>
+  </si>
+  <si>
+    <t>三軒家西</t>
+    <rPh sb="0" eb="4">
+      <t>サンゲンヤニシ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>泉尾</t>
+    <rPh sb="0" eb="2">
+      <t>イズオ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>三軒家東</t>
+    <rPh sb="0" eb="4">
+      <t>サンゲンヤヒガシ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>駅前</t>
+    <rPh sb="0" eb="2">
+      <t>エキマエ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>平尾</t>
+    <rPh sb="0" eb="2">
+      <t>ヒラオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>store-11</t>
+  </si>
+  <si>
+    <t>store-12</t>
+  </si>
+  <si>
+    <t>store-13</t>
+  </si>
+  <si>
+    <t>store-14</t>
+  </si>
+  <si>
+    <t>store-15</t>
+  </si>
+  <si>
+    <t>store-16</t>
+  </si>
+  <si>
+    <t>store-17</t>
+  </si>
+  <si>
+    <t>store-18</t>
+  </si>
+  <si>
+    <t>store-19</t>
+  </si>
+  <si>
+    <t>store-20</t>
+  </si>
+  <si>
+    <t>store-21</t>
+  </si>
+  <si>
+    <t>store-22</t>
+  </si>
+  <si>
+    <t>store-23</t>
+  </si>
+  <si>
+    <t>store-24</t>
+  </si>
+  <si>
+    <t>store-25</t>
+  </si>
+  <si>
+    <t>store-26</t>
+  </si>
+  <si>
+    <t>store-27</t>
+  </si>
+  <si>
+    <t>store-28</t>
+  </si>
+  <si>
+    <t>store-29</t>
+  </si>
+  <si>
+    <t>store-30</t>
+  </si>
+  <si>
+    <t>store-31</t>
+  </si>
+  <si>
+    <t>store-32</t>
+  </si>
+  <si>
+    <t>store-33</t>
+  </si>
+  <si>
+    <t>ハンバーガー酒場</t>
+    <rPh sb="6" eb="8">
+      <t>サカバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジビエ肉</t>
+    <rPh sb="3" eb="4">
+      <t>ニク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カフェ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BAR</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>串焼き・鉄板焼き</t>
+    <rPh sb="0" eb="2">
+      <t>クシヤ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>テッパンヤ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>焼肉・ホルモン</t>
+    <rPh sb="0" eb="2">
+      <t>ヤキニク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>居酒屋</t>
+    <rPh sb="0" eb="3">
+      <t>イザカヤ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>立ち飲み</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鶏料理</t>
+    <rPh sb="0" eb="3">
+      <t>トリリョウリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おばんざい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スナック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ダイニング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>食事</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はしご</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>てぃーようび</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>イベント限定ミニバーガー+ドリンク1杯</t>
+  </si>
+  <si>
+    <t>和牛のすじ煮込み+ドリンク1杯</t>
+    <rPh sb="14" eb="15">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒糖焼酎とニラ玉</t>
+  </si>
+  <si>
+    <t>ラム肉ショルダーステーキ(小)+飲み放題用メニューより1杯</t>
+  </si>
+  <si>
+    <t>ハンドドリップコーヒー+クレープ(チョコバナナ or ビスケットキャラメル)</t>
+  </si>
+  <si>
+    <t>限定カクテル</t>
+  </si>
+  <si>
+    <t>ちょっとミックスナッツ or ちょっとピスタチオ + ドリンク1杯(ウイスキー or 焼酎)</t>
+  </si>
+  <si>
+    <t>大根を美味しく炊いたやつの天ぷら or ちゃぼの肉豆腐＋国産鶏の出汁煮 + ドリンク1杯</t>
+    <rPh sb="43" eb="44">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本酒1杯とおつまみ</t>
+  </si>
+  <si>
+    <t>おばんざい2種盛り+ドリンク1杯(460円以内)</t>
+    <rPh sb="15" eb="16">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>串カツ5本盛り+ドリンク1杯(550円以内)</t>
+    <rPh sb="13" eb="14">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>唐揚げハーフ(2個)+ドリンク1杯</t>
+  </si>
+  <si>
+    <t>炭火焼き(小)+ドリンク1杯(495円以内)</t>
+    <rPh sb="0" eb="3">
+      <t>スミビヤ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沖縄前菜肴盛セット+ドリンク2杯（生ビール、ハイボール、泡盛（3種類から選べます）、二階堂、黒霧、酎ハイ）</t>
+  </si>
+  <si>
+    <t>おばんざい2種+ドリンク1杯(日本酒、一部銘柄を除く)</t>
+    <rPh sb="15" eb="18">
+      <t>ニホンシュ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>メイガラ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おつまみ2品+ドリンク1杯(1000円以内 )</t>
+    <rPh sb="12" eb="13">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>串3本+ドリンク1杯</t>
+    <rPh sb="9" eb="10">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">おつまみ2品盛り+ドリンク1杯(350円以内) </t>
+  </si>
+  <si>
+    <t>鉄板2種盛り+ドリンク1杯(ビール・ハイボール・酎ハイ)</t>
+    <rPh sb="12" eb="13">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おばんざい3種+ハイボールor酎ハイ</t>
+  </si>
+  <si>
+    <t>チヂミ・キムチ・ナムルセット+ドリンク1杯(550円以内)</t>
+    <rPh sb="20" eb="21">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カラオケ1時間+1品+ドリンク1杯　(20時以降限定)</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ジイコウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日替わりでおばんざい2皿+ドリンク1杯</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サラ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1品(お刺身や焼き物)+ドリンク1杯</t>
+    <rPh sb="1" eb="2">
+      <t>ヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サシミ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャーム+ドリンク1杯(700円まで)</t>
+  </si>
+  <si>
+    <t>チャーム+お菓子1袋+ドリンク1杯</t>
+    <rPh sb="16" eb="17">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選べるお好きな小鉢3品+ドリンク1杯(アサヒスーパードライ、オリオンビール、ブラックニッカハイボールのいずれか)</t>
+    <rPh sb="17" eb="18">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1時間飲み放題+歌い放題(ドリンク制限あり)</t>
+    <rPh sb="1" eb="3">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホウダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウタ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウダイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴーヤのお浸し+豚バラ軟骨塩煮込み+ドリンク1杯(瓶ビール以外)</t>
+    <rPh sb="23" eb="24">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ビン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>洋食前菜の3種盛+ドリンク1杯(限定メニューより)</t>
+  </si>
+  <si>
+    <t>ミニ前菜盛り合わせ+ドリンク1杯(ビール、ワイン、酎ハイ)</t>
+  </si>
+  <si>
+    <t>スタッフと楽しい酔いどれチンチロチャンス！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成功：会心の1杯サービス、失敗：大魔王のショット(ちょっと)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不要</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遊べる・エンタメ</t>
+  </si>
+  <si>
+    <t>ひと休み</t>
+  </si>
+  <si>
+    <t>002.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>21.jpg</t>
+  </si>
+  <si>
+    <t>22.jpg</t>
+  </si>
+  <si>
+    <t>23.jpg</t>
+  </si>
+  <si>
+    <t>24.jpg</t>
+  </si>
+  <si>
+    <t>25.jpg</t>
+  </si>
+  <si>
+    <t>26.jpg</t>
+  </si>
+  <si>
+    <t>27.jpg</t>
+  </si>
+  <si>
+    <t>28.jpg</t>
+  </si>
+  <si>
+    <t>29.jpg</t>
+  </si>
+  <si>
+    <t>30.jpg</t>
+  </si>
+  <si>
+    <t>31.jpg</t>
+  </si>
+  <si>
+    <t>32.jpg</t>
+  </si>
+  <si>
+    <t>33.jpg</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hamburger.mama</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sunnasubi0675085821</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/taipan_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haiena_haitu</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chweets_1138</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_ks_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_six_nine_0692</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chabo_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fujiwarakun_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hige_to.boin</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_sei</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_tasuichi</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jidoru_1013</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nanchatteino_erie</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/Neboke_bar</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nicoya1203</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/showz0069</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tarochan_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/teppanyaki_eihachi</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ura_omote.shokudou</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakiniku.k2plus</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moon.3.3.3</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ebisuya.taisyo</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sanchan.o2</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/soundbar__hanaichi</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/za.okinawa</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/essence_taishou</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_cococolor_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fuku__nchu</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tms_diner_osaka</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pizzerialegare</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,6 +1646,34 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -636,7 +1707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -649,6 +1720,20 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -951,6 +2036,1355 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="82.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="62.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="41.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="37.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="60" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="39.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="8">
+        <v>1000</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W10" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="X10" s="8" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W12" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="X12" s="8" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W13" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="X13" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="X14" s="8" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W15" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="X15" s="8" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="X16" s="8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="X17" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="X18" s="8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W19" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="X19" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>300</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="W20" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="X20" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W21" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="X21" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W22" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="X22" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W23" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="X23" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W24" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="X24" s="8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W25" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="X25" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W26" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="X26" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W27" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="X27" s="8" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W28" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="X28" s="8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W29" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="X29" s="8" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W30" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="X30" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W31" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="X31" s="8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W32" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="X32" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W33" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="X33" s="8" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W34" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="X34" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0041B99-7380-446F-B4E9-E02884CC4E53}">
   <dimension ref="A1:X11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1734,36 +4168,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>
--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hinam\OneDrive\Documents\CHWEETS\013_大正よいどれ\006.LINEアプリ\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1235884-C1F9-4C56-AF5A-0B9EFD68F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174367B7-DE46-420E-8DF9-C70F3A0AAC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1415,99 +1415,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>3.jpg</t>
-  </si>
-  <si>
-    <t>4.jpg</t>
-  </si>
-  <si>
-    <t>5.jpg</t>
-  </si>
-  <si>
-    <t>6.jpg</t>
-  </si>
-  <si>
-    <t>7.jpg</t>
-  </si>
-  <si>
-    <t>8.jpg</t>
-  </si>
-  <si>
-    <t>9.jpg</t>
-  </si>
-  <si>
-    <t>10.jpg</t>
-  </si>
-  <si>
-    <t>11.jpg</t>
-  </si>
-  <si>
-    <t>12.jpg</t>
-  </si>
-  <si>
-    <t>13.jpg</t>
-  </si>
-  <si>
-    <t>14.jpg</t>
-  </si>
-  <si>
-    <t>15.jpg</t>
-  </si>
-  <si>
-    <t>16.jpg</t>
-  </si>
-  <si>
-    <t>17.jpg</t>
-  </si>
-  <si>
-    <t>18.jpg</t>
-  </si>
-  <si>
-    <t>19.jpg</t>
-  </si>
-  <si>
-    <t>20.jpg</t>
-  </si>
-  <si>
-    <t>21.jpg</t>
-  </si>
-  <si>
-    <t>22.jpg</t>
-  </si>
-  <si>
-    <t>23.jpg</t>
-  </si>
-  <si>
-    <t>24.jpg</t>
-  </si>
-  <si>
-    <t>25.jpg</t>
-  </si>
-  <si>
-    <t>26.jpg</t>
-  </si>
-  <si>
-    <t>27.jpg</t>
-  </si>
-  <si>
-    <t>28.jpg</t>
-  </si>
-  <si>
-    <t>29.jpg</t>
-  </si>
-  <si>
-    <t>30.jpg</t>
-  </si>
-  <si>
-    <t>31.jpg</t>
-  </si>
-  <si>
-    <t>32.jpg</t>
-  </si>
-  <si>
-    <t>33.jpg</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/hamburger.mama</t>
   </si>
   <si>
@@ -1602,6 +1509,101 @@
   </si>
   <si>
     <t>https://www.instagram.com/pizzerialegare</t>
+  </si>
+  <si>
+    <t>003.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>005.jpg</t>
+  </si>
+  <si>
+    <t>006.jpg</t>
+  </si>
+  <si>
+    <t>007.jpg</t>
+  </si>
+  <si>
+    <t>008.jpg</t>
+  </si>
+  <si>
+    <t>009.jpg</t>
+  </si>
+  <si>
+    <t>010.jpg</t>
+  </si>
+  <si>
+    <t>011.jpg</t>
+  </si>
+  <si>
+    <t>012.jpg</t>
+  </si>
+  <si>
+    <t>013.jpg</t>
+  </si>
+  <si>
+    <t>014.jpg</t>
+  </si>
+  <si>
+    <t>015.jpg</t>
+  </si>
+  <si>
+    <t>016.jpg</t>
+  </si>
+  <si>
+    <t>017.jpg</t>
+  </si>
+  <si>
+    <t>018.jpg</t>
+  </si>
+  <si>
+    <t>019.jpg</t>
+  </si>
+  <si>
+    <t>020.jpg</t>
+  </si>
+  <si>
+    <t>021.jpg</t>
+  </si>
+  <si>
+    <t>022.jpg</t>
+  </si>
+  <si>
+    <t>023.jpg</t>
+  </si>
+  <si>
+    <t>024.jpg</t>
+  </si>
+  <si>
+    <t>025.jpg</t>
+  </si>
+  <si>
+    <t>026.jpg</t>
+  </si>
+  <si>
+    <t>027.jpg</t>
+  </si>
+  <si>
+    <t>028.jpg</t>
+  </si>
+  <si>
+    <t>029.jpg</t>
+  </si>
+  <si>
+    <t>030.jpg</t>
+  </si>
+  <si>
+    <t>031.jpg</t>
+  </si>
+  <si>
+    <t>032.jpg</t>
+  </si>
+  <si>
+    <t>033.jpg</t>
+  </si>
+  <si>
+    <t>004.jpg</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1707,7 +1709,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1734,6 +1736,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2210,7 +2213,7 @@
       <c r="W2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="12" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2243,9 +2246,9 @@
         <v>35</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="X3" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="X3" s="12" t="s">
         <v>322</v>
       </c>
     </row>
@@ -2278,10 +2281,10 @@
         <v>35</v>
       </c>
       <c r="W4" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="X4" s="12" t="s">
         <v>355</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2313,10 +2316,10 @@
         <v>35</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2348,10 +2351,10 @@
         <v>35</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="X6" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
+      </c>
+      <c r="X6" s="12" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2383,10 +2386,10 @@
         <v>35</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2418,10 +2421,10 @@
         <v>35</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2453,10 +2456,10 @@
         <v>35</v>
       </c>
       <c r="W9" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="X9" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
+      </c>
+      <c r="X9" s="12" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2488,10 +2491,10 @@
         <v>35</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="X10" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
+      </c>
+      <c r="X10" s="12" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2523,10 +2526,10 @@
         <v>35</v>
       </c>
       <c r="W11" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="X11" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
+      </c>
+      <c r="X11" s="12" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -2558,10 +2561,10 @@
         <v>35</v>
       </c>
       <c r="W12" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="X12" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
+      </c>
+      <c r="X12" s="12" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -2593,10 +2596,10 @@
         <v>35</v>
       </c>
       <c r="W13" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="X13" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
+      </c>
+      <c r="X13" s="12" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2628,10 +2631,10 @@
         <v>35</v>
       </c>
       <c r="W14" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="X14" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
+      </c>
+      <c r="X14" s="12" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2663,10 +2666,10 @@
         <v>35</v>
       </c>
       <c r="W15" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="X15" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
+      </c>
+      <c r="X15" s="12" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -2698,10 +2701,10 @@
         <v>35</v>
       </c>
       <c r="W16" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="X16" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="X16" s="12" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2733,10 +2736,10 @@
         <v>35</v>
       </c>
       <c r="W17" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="X17" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
+      </c>
+      <c r="X17" s="12" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -2768,10 +2771,10 @@
         <v>35</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="X18" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="X18" s="12" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -2803,10 +2806,10 @@
         <v>35</v>
       </c>
       <c r="W19" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="X19" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
+      </c>
+      <c r="X19" s="12" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -2847,10 +2850,10 @@
         <v>318</v>
       </c>
       <c r="W20" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="X20" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
+      </c>
+      <c r="X20" s="12" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2882,10 +2885,10 @@
         <v>35</v>
       </c>
       <c r="W21" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="X21" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
+      </c>
+      <c r="X21" s="12" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -2917,10 +2920,10 @@
         <v>35</v>
       </c>
       <c r="W22" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="X22" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="X22" s="12" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -2952,10 +2955,10 @@
         <v>35</v>
       </c>
       <c r="W23" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="X23" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
+      </c>
+      <c r="X23" s="12" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -2987,10 +2990,10 @@
         <v>35</v>
       </c>
       <c r="W24" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="X24" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
+      </c>
+      <c r="X24" s="12" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -3022,10 +3025,10 @@
         <v>35</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="X25" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
+      </c>
+      <c r="X25" s="12" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -3057,10 +3060,10 @@
         <v>35</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="X26" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
+      </c>
+      <c r="X26" s="12" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -3092,10 +3095,10 @@
         <v>35</v>
       </c>
       <c r="W27" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="X27" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
+      </c>
+      <c r="X27" s="12" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -3127,10 +3130,10 @@
         <v>35</v>
       </c>
       <c r="W28" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="X28" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
+      </c>
+      <c r="X28" s="12" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -3162,10 +3165,10 @@
         <v>35</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="X29" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="X29" s="12" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -3197,10 +3200,10 @@
         <v>35</v>
       </c>
       <c r="W30" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="X30" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
+      </c>
+      <c r="X30" s="12" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -3232,10 +3235,10 @@
         <v>35</v>
       </c>
       <c r="W31" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="X31" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
+      </c>
+      <c r="X31" s="12" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -3267,10 +3270,10 @@
         <v>35</v>
       </c>
       <c r="W32" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="X32" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
+      </c>
+      <c r="X32" s="12" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -3302,10 +3305,10 @@
         <v>35</v>
       </c>
       <c r="W33" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="X33" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+      <c r="X33" s="12" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3337,10 +3340,10 @@
         <v>35</v>
       </c>
       <c r="W34" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="X34" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
+      </c>
+      <c r="X34" s="12" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hinam\OneDrive\Documents\CHWEETS\013_大正よいどれ\006.LINEアプリ\yoidore-quest2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174367B7-DE46-420E-8DF9-C70F3A0AAC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6734A1-784B-451B-ADF9-B472BB207DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7230" yWindow="2550" windowWidth="21570" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="店舗一覧" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="店舗一覧 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">店舗一覧!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">店舗一覧!$A$1:$W$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="418">
   <si>
     <t>ID</t>
   </si>
@@ -701,22 +701,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>串カツ・牡蠣・沖縄料理</t>
-    <rPh sb="0" eb="1">
-      <t>クシ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>オキナワ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>リョウリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>居酒屋たすいち</t>
     <rPh sb="0" eb="3">
       <t>イザカヤ</t>
@@ -1138,10 +1122,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>てぃーようび</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>イベント限定ミニバーガー+ドリンク1杯</t>
   </si>
   <si>
@@ -1604,6 +1584,109 @@
   <si>
     <t>004.jpg</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>logo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>001.png</t>
+  </si>
+  <si>
+    <t>002.png</t>
+  </si>
+  <si>
+    <t>003.png</t>
+  </si>
+  <si>
+    <t>004.png</t>
+  </si>
+  <si>
+    <t>005.png</t>
+  </si>
+  <si>
+    <t>006.png</t>
+  </si>
+  <si>
+    <t>007.png</t>
+  </si>
+  <si>
+    <t>008.png</t>
+  </si>
+  <si>
+    <t>009.png</t>
+  </si>
+  <si>
+    <t>010.png</t>
+  </si>
+  <si>
+    <t>011.png</t>
+  </si>
+  <si>
+    <t>012.png</t>
+  </si>
+  <si>
+    <t>013.png</t>
+  </si>
+  <si>
+    <t>014.png</t>
+  </si>
+  <si>
+    <t>015.png</t>
+  </si>
+  <si>
+    <t>016.png</t>
+  </si>
+  <si>
+    <t>017.png</t>
+  </si>
+  <si>
+    <t>018.png</t>
+  </si>
+  <si>
+    <t>019.png</t>
+  </si>
+  <si>
+    <t>020.png</t>
+  </si>
+  <si>
+    <t>021.png</t>
+  </si>
+  <si>
+    <t>022.png</t>
+  </si>
+  <si>
+    <t>023.png</t>
+  </si>
+  <si>
+    <t>024.png</t>
+  </si>
+  <si>
+    <t>025.png</t>
+  </si>
+  <si>
+    <t>026.png</t>
+  </si>
+  <si>
+    <t>027.png</t>
+  </si>
+  <si>
+    <t>028.png</t>
+  </si>
+  <si>
+    <t>029.png</t>
+  </si>
+  <si>
+    <t>030.png</t>
+  </si>
+  <si>
+    <t>031.png</t>
+  </si>
+  <si>
+    <t>032.png</t>
+  </si>
+  <si>
+    <t>033.png</t>
   </si>
 </sst>
 </file>
@@ -2044,29 +2127,28 @@
   <cols>
     <col min="1" max="1" width="9.5" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="54.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="82.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="62.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="41.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="37.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="60" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="39.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="8"/>
+    <col min="3" max="3" width="9.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="82.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="50.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="60" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="39.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2077,70 +2159,70 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>23</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2150,71 +2232,71 @@
       <c r="B2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>243</v>
+      <c r="C2" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>28</v>
+        <v>282</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>283</v>
+        <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="8">
+      <c r="I2" s="8">
         <v>1000</v>
       </c>
+      <c r="J2" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="K2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
       <c r="R2" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" s="8" t="s">
         <v>44</v>
       </c>
+      <c r="W2" s="12" t="s">
+        <v>45</v>
+      </c>
       <c r="X2" s="12" t="s">
-        <v>45</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2224,32 +2306,35 @@
       <c r="B3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>245</v>
+      <c r="C3" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>286</v>
+      <c r="K3" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="8" t="s">
-        <v>323</v>
+      <c r="V3" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>320</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>322</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2259,32 +2344,35 @@
       <c r="B4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>246</v>
+      <c r="C4" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>283</v>
+        <v>182</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W4" s="8" t="s">
-        <v>324</v>
+      <c r="V4" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>353</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2294,32 +2382,35 @@
       <c r="B5" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>246</v>
+      <c r="C5" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>284</v>
+        <v>184</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W5" s="8" t="s">
-        <v>325</v>
+      <c r="V5" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2329,32 +2420,35 @@
       <c r="B6" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>243</v>
+      <c r="C6" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>283</v>
+        <v>186</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W6" s="8" t="s">
-        <v>326</v>
+      <c r="V6" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2364,32 +2458,35 @@
       <c r="B7" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>321</v>
+      <c r="C7" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W7" s="8" t="s">
-        <v>327</v>
+      <c r="V7" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2399,32 +2496,35 @@
       <c r="B8" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>320</v>
+      <c r="C8" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W8" s="8" t="s">
-        <v>328</v>
+      <c r="V8" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="W8" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2434,32 +2534,35 @@
       <c r="B9" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>320</v>
+      <c r="C9" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W9" s="8" t="s">
-        <v>329</v>
+      <c r="V9" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="W9" s="12" t="s">
+        <v>357</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2469,32 +2572,35 @@
       <c r="B10" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>245</v>
+      <c r="C10" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W10" s="8" t="s">
-        <v>330</v>
+      <c r="V10" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="W10" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2504,850 +2610,922 @@
       <c r="B11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>243</v>
+      <c r="C11" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>276</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>283</v>
+        <v>196</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W11" s="8" t="s">
-        <v>331</v>
+      <c r="V11" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="W11" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>246</v>
+      <c r="C12" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W12" s="8" t="s">
-        <v>332</v>
+      <c r="V12" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="W12" s="12" t="s">
+        <v>360</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>245</v>
+      <c r="C13" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>276</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
+      </c>
+      <c r="F13" s="8">
+        <v>120</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W13" s="8" t="s">
-        <v>333</v>
+      <c r="V13" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="W13" s="12" t="s">
+        <v>361</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G14" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W14" s="8" t="s">
-        <v>334</v>
+      <c r="V14" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="W14" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W15" s="8" t="s">
-        <v>335</v>
+      <c r="V15" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="W15" s="12" t="s">
+        <v>363</v>
       </c>
       <c r="X15" s="12" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G16" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W16" s="8" t="s">
-        <v>336</v>
+      <c r="V16" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="X16" s="12" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G17" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W17" s="8" t="s">
-        <v>337</v>
+      <c r="V17" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="W17" s="12" t="s">
+        <v>365</v>
       </c>
       <c r="X17" s="12" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>321</v>
-      </c>
       <c r="G18" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W18" s="8" t="s">
-        <v>338</v>
+      <c r="V18" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="W18" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G19" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W19" s="8" t="s">
-        <v>339</v>
+      <c r="V19" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="X19" s="12" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>214</v>
+      <c r="K20" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="P20" s="8">
         <v>300</v>
       </c>
+      <c r="Q20" s="8" t="s">
+        <v>317</v>
+      </c>
       <c r="R20" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="T20" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="W20" s="8" t="s">
-        <v>340</v>
+        <v>315</v>
+      </c>
+      <c r="S20" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="W20" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="X20" s="12" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G21" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W21" s="8" t="s">
-        <v>341</v>
+      <c r="V21" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="W21" s="12" t="s">
+        <v>369</v>
       </c>
       <c r="X21" s="12" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G22" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W22" s="8" t="s">
-        <v>342</v>
+      <c r="V22" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="W22" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="X22" s="12" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G23" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M23" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W23" s="8" t="s">
-        <v>343</v>
+      <c r="V23" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="W23" s="12" t="s">
+        <v>371</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G24" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W24" s="8" t="s">
-        <v>344</v>
+      <c r="V24" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="W24" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G25" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W25" s="8" t="s">
-        <v>345</v>
+      <c r="V25" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="W25" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G26" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M26" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W26" s="8" t="s">
-        <v>346</v>
+      <c r="V26" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G27" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M27" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W27" s="8" t="s">
-        <v>347</v>
+      <c r="V27" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>375</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>320</v>
-      </c>
       <c r="G28" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W28" s="8" t="s">
-        <v>348</v>
+      <c r="V28" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="W28" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G29" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M29" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="8" t="s">
-        <v>349</v>
+      <c r="V29" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="W29" s="12" t="s">
+        <v>377</v>
       </c>
       <c r="X29" s="12" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M30" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W30" s="8" t="s">
-        <v>350</v>
+      <c r="V30" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>378</v>
       </c>
       <c r="X30" s="12" t="s">
-        <v>380</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>320</v>
-      </c>
       <c r="G31" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W31" s="8" t="s">
-        <v>351</v>
+      <c r="V31" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="W31" s="12" t="s">
+        <v>379</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B32" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="G32" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M32" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W32" s="8" t="s">
-        <v>352</v>
+      <c r="V32" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="W32" s="12" t="s">
+        <v>380</v>
       </c>
       <c r="X32" s="12" t="s">
-        <v>382</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="G33" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M33" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W33" s="8" t="s">
-        <v>353</v>
+      <c r="V33" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="W33" s="12" t="s">
+        <v>381</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>282</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M34" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="W34" s="8" t="s">
-        <v>354</v>
+      <c r="V34" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="W34" s="12" t="s">
+        <v>382</v>
       </c>
       <c r="X34" s="12" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6734A1-784B-451B-ADF9-B472BB207DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758C803F-A0FE-47CB-99B4-201CC32525C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7230" yWindow="2550" windowWidth="21570" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="店舗一覧" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="448">
   <si>
     <t>ID</t>
   </si>
@@ -769,9 +769,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Barカセット</t>
-  </si>
-  <si>
     <t>80's・ロック・駄菓子</t>
     <rPh sb="9" eb="12">
       <t>ダガシ</t>
@@ -856,9 +853,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>呑笑戎屋</t>
-  </si>
-  <si>
     <t>地元親子の大衆居酒屋</t>
   </si>
   <si>
@@ -1687,6 +1681,134 @@
   </si>
   <si>
     <t>033.png</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LvrTR4thHgoGpoRc7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9DHWbdXcG6VwQRg17</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wSUzPpSDHh3tzyap6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PB2QxJm3seTe8PFH6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Prnu5oBX6hyQzpft6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/95uXqnFcfkMM8Jwo8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NL1uEH8kq3MhMEzdA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rc5NfzqfDAM7pevWA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DXhUb1vmR7aNUMMT8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9Wt44gRpXPDoTt1q9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Barカセット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/e85zQpDRWme5xsyr6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qM8P7SU6UqcARZm29</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>呑笑戎屋</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1792,7 +1914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1815,11 +1937,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2126,26 +2247,11 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="82.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="50.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="37.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="60" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="10.5" style="8" customWidth="1"/>
+    <col min="19" max="19" width="10.5" style="12" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="8" customWidth="1"/>
+    <col min="21" max="21" width="44.5" style="8" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="39.25" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.625" style="8" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="8"/>
@@ -2222,7 +2328,7 @@
         <v>23</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2233,13 +2339,13 @@
         <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>30</v>
@@ -2280,7 +2386,7 @@
       <c r="R2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="12" t="s">
         <v>41</v>
       </c>
       <c r="T2" s="8" t="s">
@@ -2292,11 +2398,11 @@
       <c r="V2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="12" t="s">
-        <v>385</v>
+      <c r="X2" s="11" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2307,19 +2413,19 @@
         <v>179</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>34</v>
@@ -2327,14 +2433,17 @@
       <c r="L3" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U3" s="13" t="s">
+        <v>416</v>
+      </c>
       <c r="V3" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="X3" s="12" t="s">
-        <v>386</v>
+        <v>319</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2345,19 +2454,19 @@
         <v>181</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>34</v>
@@ -2365,14 +2474,17 @@
       <c r="L4" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U4" s="13" t="s">
+        <v>417</v>
+      </c>
       <c r="V4" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="W4" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="X4" s="12" t="s">
-        <v>387</v>
+        <v>320</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2383,19 +2495,19 @@
         <v>183</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>34</v>
@@ -2403,14 +2515,17 @@
       <c r="L5" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U5" s="13" t="s">
+        <v>418</v>
+      </c>
       <c r="V5" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="X5" s="12" t="s">
-        <v>388</v>
+        <v>321</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2421,19 +2536,19 @@
         <v>185</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>34</v>
@@ -2441,14 +2556,17 @@
       <c r="L6" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U6" s="13" t="s">
+        <v>419</v>
+      </c>
       <c r="V6" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="X6" s="12" t="s">
-        <v>389</v>
+        <v>322</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2459,19 +2577,19 @@
         <v>187</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>319</v>
+        <v>270</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>188</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>34</v>
@@ -2479,14 +2597,17 @@
       <c r="L7" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U7" s="13" t="s">
+        <v>420</v>
+      </c>
       <c r="V7" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>390</v>
+        <v>323</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2497,19 +2618,19 @@
         <v>189</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>318</v>
+        <v>271</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>190</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>34</v>
@@ -2517,14 +2638,17 @@
       <c r="L8" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U8" s="13" t="s">
+        <v>421</v>
+      </c>
       <c r="V8" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="W8" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="X8" s="12" t="s">
-        <v>391</v>
+        <v>324</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2535,19 +2659,19 @@
         <v>191</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>318</v>
+        <v>271</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>34</v>
@@ -2555,14 +2679,17 @@
       <c r="L9" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U9" s="13" t="s">
+        <v>435</v>
+      </c>
       <c r="V9" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="X9" s="12" t="s">
-        <v>392</v>
+        <v>325</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2573,19 +2700,19 @@
         <v>193</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>194</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>34</v>
@@ -2593,14 +2720,17 @@
       <c r="L10" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U10" s="13" t="s">
+        <v>436</v>
+      </c>
       <c r="V10" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>393</v>
+        <v>326</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2611,19 +2741,19 @@
         <v>195</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>196</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>34</v>
@@ -2631,37 +2761,40 @@
       <c r="L11" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U11" s="13" t="s">
+        <v>441</v>
+      </c>
       <c r="V11" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="X11" s="12" t="s">
-        <v>394</v>
+        <v>327</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>197</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>34</v>
@@ -2669,37 +2802,40 @@
       <c r="L12" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U12" s="13" t="s">
+        <v>434</v>
+      </c>
       <c r="V12" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="W12" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="X12" s="12" t="s">
-        <v>395</v>
+        <v>328</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F13" s="8">
         <v>120</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>34</v>
@@ -2707,37 +2843,40 @@
       <c r="L13" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U13" s="13" t="s">
+        <v>428</v>
+      </c>
       <c r="V13" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="W13" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="X13" s="12" t="s">
-        <v>396</v>
+        <v>329</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>200</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>201</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>34</v>
@@ -2745,37 +2884,40 @@
       <c r="L14" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U14" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="V14" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="W14" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>397</v>
+        <v>330</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>203</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>34</v>
@@ -2783,37 +2925,40 @@
       <c r="L15" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U15" s="13" t="s">
+        <v>429</v>
+      </c>
       <c r="V15" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="W15" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>398</v>
+        <v>331</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>205</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>34</v>
@@ -2821,37 +2966,40 @@
       <c r="L16" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U16" s="13" t="s">
+        <v>444</v>
+      </c>
       <c r="V16" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="W16" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="X16" s="12" t="s">
-        <v>399</v>
+        <v>332</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>207</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>34</v>
@@ -2859,37 +3007,40 @@
       <c r="L17" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U17" s="13" t="s">
+        <v>438</v>
+      </c>
       <c r="V17" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="W17" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="X17" s="12" t="s">
-        <v>400</v>
+        <v>333</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>208</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>319</v>
+        <v>271</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>209</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>34</v>
@@ -2897,37 +3048,40 @@
       <c r="L18" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U18" s="13" t="s">
+        <v>430</v>
+      </c>
       <c r="V18" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="W18" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="X18" s="12" t="s">
-        <v>401</v>
+        <v>334</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>211</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>34</v>
@@ -2935,34 +3089,37 @@
       <c r="L19" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U19" s="13" t="s">
+        <v>439</v>
+      </c>
       <c r="V19" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="X19" s="12" t="s">
-        <v>402</v>
+        <v>335</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>213</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>34</v>
@@ -2974,45 +3131,48 @@
         <v>300</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="S20" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="U20" s="13" t="s">
+        <v>442</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="W20" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="X20" s="12" t="s">
-        <v>403</v>
+        <v>336</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="G21" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>34</v>
@@ -3020,37 +3180,40 @@
       <c r="L21" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U21" s="13" t="s">
+        <v>440</v>
+      </c>
       <c r="V21" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="W21" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="X21" s="12" t="s">
-        <v>404</v>
+        <v>337</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>217</v>
-      </c>
       <c r="G22" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>34</v>
@@ -3058,37 +3221,40 @@
       <c r="L22" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U22" s="13" t="s">
+        <v>437</v>
+      </c>
       <c r="V22" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="W22" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="X22" s="12" t="s">
-        <v>405</v>
+        <v>338</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>219</v>
-      </c>
       <c r="G23" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>34</v>
@@ -3096,37 +3262,40 @@
       <c r="L23" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U23" s="13" t="s">
+        <v>431</v>
+      </c>
       <c r="V23" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="X23" s="12" t="s">
-        <v>406</v>
+        <v>339</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="G24" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>34</v>
@@ -3134,37 +3303,40 @@
       <c r="L24" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U24" s="13" t="s">
+        <v>433</v>
+      </c>
       <c r="V24" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="W24" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="X24" s="12" t="s">
-        <v>407</v>
+        <v>340</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="G25" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>34</v>
@@ -3173,36 +3345,36 @@
         <v>35</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="W25" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="X25" s="12" t="s">
-        <v>408</v>
+        <v>341</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>224</v>
+        <v>447</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>34</v>
@@ -3211,36 +3383,36 @@
         <v>35</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="X26" s="12" t="s">
-        <v>409</v>
+        <v>342</v>
+      </c>
+      <c r="W26" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>34</v>
@@ -3248,37 +3420,40 @@
       <c r="L27" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U27" s="13" t="s">
+        <v>432</v>
+      </c>
       <c r="V27" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="X27" s="12" t="s">
-        <v>410</v>
+        <v>343</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>318</v>
+        <v>278</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>34</v>
@@ -3286,37 +3461,40 @@
       <c r="L28" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U28" s="13" t="s">
+        <v>427</v>
+      </c>
       <c r="V28" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="W28" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="X28" s="12" t="s">
-        <v>411</v>
+        <v>344</v>
+      </c>
+      <c r="W28" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>34</v>
@@ -3324,37 +3502,40 @@
       <c r="L29" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U29" s="13" t="s">
+        <v>424</v>
+      </c>
       <c r="V29" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="W29" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="X29" s="12" t="s">
-        <v>412</v>
+        <v>345</v>
+      </c>
+      <c r="W29" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="X29" s="11" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>34</v>
@@ -3362,37 +3543,40 @@
       <c r="L30" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U30" s="13" t="s">
+        <v>426</v>
+      </c>
       <c r="V30" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="W30" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="X30" s="12" t="s">
-        <v>413</v>
+        <v>346</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="X30" s="11" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>318</v>
+        <v>271</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>34</v>
@@ -3400,37 +3584,40 @@
       <c r="L31" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U31" s="13" t="s">
+        <v>425</v>
+      </c>
       <c r="V31" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="W31" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="X31" s="12" t="s">
-        <v>414</v>
+        <v>347</v>
+      </c>
+      <c r="W31" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="X31" s="11" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>34</v>
@@ -3438,37 +3625,40 @@
       <c r="L32" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U32" s="13" t="s">
+        <v>423</v>
+      </c>
       <c r="V32" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="W32" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="X32" s="12" t="s">
-        <v>415</v>
+        <v>348</v>
+      </c>
+      <c r="W32" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="X32" s="11" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D33" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="F33" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>34</v>
@@ -3476,37 +3666,40 @@
       <c r="L33" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U33" s="13" t="s">
+        <v>446</v>
+      </c>
       <c r="V33" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="W33" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="X33" s="12" t="s">
-        <v>416</v>
+        <v>349</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="X33" s="11" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K34" s="8" t="s">
         <v>34</v>
@@ -3514,14 +3707,17 @@
       <c r="L34" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="U34" s="13" t="s">
+        <v>445</v>
+      </c>
       <c r="V34" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="W34" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="X34" s="12" t="s">
-        <v>417</v>
+        <v>350</v>
+      </c>
+      <c r="W34" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="X34" s="11" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758C803F-A0FE-47CB-99B4-201CC32525C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8D8FAF-E250-4EBA-92D3-AC4122A41423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="483">
   <si>
     <t>ID</t>
   </si>
@@ -1108,14 +1108,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>食事</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>はしご</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>イベント限定ミニバーガー+ドリンク1杯</t>
   </si>
   <si>
@@ -1382,432 +1374,562 @@
     <t>遊べる・エンタメ</t>
   </si>
   <si>
+    <t>002.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hamburger.mama</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sunnasubi0675085821</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/taipan_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haiena_haitu</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chweets_1138</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_ks_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_six_nine_0692</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chabo_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fujiwarakun_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hige_to.boin</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_sei</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_tasuichi</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jidoru_1013</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nanchatteino_erie</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/Neboke_bar</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nicoya1203</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/showz0069</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tarochan_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/teppanyaki_eihachi</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ura_omote.shokudou</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakiniku.k2plus</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moon.3.3.3</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ebisuya.taisyo</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sanchan.o2</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/soundbar__hanaichi</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/za.okinawa</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/essence_taishou</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_cococolor_taisho</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fuku__nchu</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tms_diner_osaka</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pizzerialegare</t>
+  </si>
+  <si>
+    <t>003.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>005.jpg</t>
+  </si>
+  <si>
+    <t>006.jpg</t>
+  </si>
+  <si>
+    <t>007.jpg</t>
+  </si>
+  <si>
+    <t>008.jpg</t>
+  </si>
+  <si>
+    <t>009.jpg</t>
+  </si>
+  <si>
+    <t>010.jpg</t>
+  </si>
+  <si>
+    <t>011.jpg</t>
+  </si>
+  <si>
+    <t>012.jpg</t>
+  </si>
+  <si>
+    <t>013.jpg</t>
+  </si>
+  <si>
+    <t>014.jpg</t>
+  </si>
+  <si>
+    <t>015.jpg</t>
+  </si>
+  <si>
+    <t>016.jpg</t>
+  </si>
+  <si>
+    <t>017.jpg</t>
+  </si>
+  <si>
+    <t>018.jpg</t>
+  </si>
+  <si>
+    <t>019.jpg</t>
+  </si>
+  <si>
+    <t>020.jpg</t>
+  </si>
+  <si>
+    <t>021.jpg</t>
+  </si>
+  <si>
+    <t>022.jpg</t>
+  </si>
+  <si>
+    <t>023.jpg</t>
+  </si>
+  <si>
+    <t>024.jpg</t>
+  </si>
+  <si>
+    <t>025.jpg</t>
+  </si>
+  <si>
+    <t>026.jpg</t>
+  </si>
+  <si>
+    <t>027.jpg</t>
+  </si>
+  <si>
+    <t>028.jpg</t>
+  </si>
+  <si>
+    <t>029.jpg</t>
+  </si>
+  <si>
+    <t>030.jpg</t>
+  </si>
+  <si>
+    <t>031.jpg</t>
+  </si>
+  <si>
+    <t>032.jpg</t>
+  </si>
+  <si>
+    <t>033.jpg</t>
+  </si>
+  <si>
+    <t>004.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>logo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>001.png</t>
+  </si>
+  <si>
+    <t>002.png</t>
+  </si>
+  <si>
+    <t>003.png</t>
+  </si>
+  <si>
+    <t>004.png</t>
+  </si>
+  <si>
+    <t>005.png</t>
+  </si>
+  <si>
+    <t>006.png</t>
+  </si>
+  <si>
+    <t>007.png</t>
+  </si>
+  <si>
+    <t>008.png</t>
+  </si>
+  <si>
+    <t>009.png</t>
+  </si>
+  <si>
+    <t>010.png</t>
+  </si>
+  <si>
+    <t>011.png</t>
+  </si>
+  <si>
+    <t>012.png</t>
+  </si>
+  <si>
+    <t>013.png</t>
+  </si>
+  <si>
+    <t>014.png</t>
+  </si>
+  <si>
+    <t>015.png</t>
+  </si>
+  <si>
+    <t>016.png</t>
+  </si>
+  <si>
+    <t>017.png</t>
+  </si>
+  <si>
+    <t>018.png</t>
+  </si>
+  <si>
+    <t>019.png</t>
+  </si>
+  <si>
+    <t>020.png</t>
+  </si>
+  <si>
+    <t>021.png</t>
+  </si>
+  <si>
+    <t>022.png</t>
+  </si>
+  <si>
+    <t>023.png</t>
+  </si>
+  <si>
+    <t>024.png</t>
+  </si>
+  <si>
+    <t>025.png</t>
+  </si>
+  <si>
+    <t>026.png</t>
+  </si>
+  <si>
+    <t>027.png</t>
+  </si>
+  <si>
+    <t>028.png</t>
+  </si>
+  <si>
+    <t>029.png</t>
+  </si>
+  <si>
+    <t>030.png</t>
+  </si>
+  <si>
+    <t>031.png</t>
+  </si>
+  <si>
+    <t>032.png</t>
+  </si>
+  <si>
+    <t>033.png</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LvrTR4thHgoGpoRc7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9DHWbdXcG6VwQRg17</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wSUzPpSDHh3tzyap6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/PB2QxJm3seTe8PFH6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Prnu5oBX6hyQzpft6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/95uXqnFcfkMM8Jwo8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NL1uEH8kq3MhMEzdA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rc5NfzqfDAM7pevWA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DXhUb1vmR7aNUMMT8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9Wt44gRpXPDoTt1q9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Barカセット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/e85zQpDRWme5xsyr6</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qM8P7SU6UqcARZm29</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>呑笑戎屋</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>串カツ・牡蠣・沖縄料理</t>
+    <rPh sb="0" eb="1">
+      <t>クシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おばんざい三種盛り晩酌セット</t>
+  </si>
+  <si>
+    <t>どれクエ限定ミニバーガーセット</t>
+  </si>
+  <si>
+    <t>牛すじ煮込み焼肉屋の晩酌セット</t>
+  </si>
+  <si>
+    <t>黒糖焼酎とニラ玉セット</t>
+  </si>
+  <si>
+    <t>ラム肉ショルダーステーキセット</t>
+  </si>
+  <si>
+    <t>夜カフェクレープセット</t>
+  </si>
+  <si>
+    <t>限定カクテルセット</t>
+  </si>
+  <si>
+    <t>ミックスナッツ晩酌セット</t>
+  </si>
+  <si>
+    <t>ちゃぼの鶏だし満喫セット</t>
+  </si>
+  <si>
+    <t>日本酒と創作おつまみセット</t>
+  </si>
+  <si>
+    <t>おばんざい立ち飲みセット</t>
+  </si>
+  <si>
+    <t>串カツと一杯セット</t>
+  </si>
+  <si>
+    <t>唐揚げちょい飲みセット</t>
+  </si>
+  <si>
+    <t>宮崎地鶏炭火焼きセット</t>
+  </si>
+  <si>
+    <t>沖縄前菜盛り泡盛セット</t>
+  </si>
+  <si>
+    <t>昭和おばんざい晩酌セット</t>
+  </si>
+  <si>
+    <t>隠れ家おつまみセット</t>
+  </si>
+  <si>
+    <t>創作串焼き三本セット</t>
+  </si>
+  <si>
+    <t>80's駄菓子バーセット</t>
+  </si>
+  <si>
+    <t>昼飲みホルモンおつまみセット</t>
+  </si>
+  <si>
+    <t>鉄板焼き盛り合わせセット</t>
+  </si>
+  <si>
+    <t>蒸し料理おばんざいセット</t>
+  </si>
+  <si>
+    <t>韓国おつまみセット</t>
+  </si>
+  <si>
+    <t>歌って飲めるカラオケセット</t>
+  </si>
+  <si>
+    <t>日替わりおばんざいセット</t>
+  </si>
+  <si>
+    <t>海鮮一品晩酌セット</t>
+  </si>
+  <si>
+    <t>カラオケバー乾杯セット</t>
+  </si>
+  <si>
+    <t>沖縄ちょい飲みセット</t>
+  </si>
+  <si>
+    <t>沖縄小鉢三種盛りセット</t>
+  </si>
+  <si>
+    <t>歌い放題飲み放題セット</t>
+  </si>
+  <si>
+    <t>沖縄家庭料理セット</t>
+  </si>
+  <si>
+    <t>洋食前菜バルセット</t>
+  </si>
+  <si>
+    <t>ピッツァ前菜ワインセット</t>
+  </si>
+  <si>
+    <t>しっかりご飯</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サク飲み</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>ひと休み</t>
-  </si>
-  <si>
-    <t>002.jpg</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://www.instagram.com/hamburger.mama</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/sunnasubi0675085821</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/taipan_taisho</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/haiena_haitu</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/chweets_1138</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bar_ks_taisho</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bar_six_nine_0692</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/chabo_taisho</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/fujiwarakun_taisho</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/hige_to.boin</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/izakaya_sei</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/izakaya_tasuichi</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/jidoru_1013</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/nanchatteino_erie</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/Neboke_bar</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/nicoya1203</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/showz0069</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/tarochan_taisho</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/teppanyaki_eihachi</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/ura_omote.shokudou</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/yakiniku.k2plus</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/moon.3.3.3</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/ebisuya.taisyo</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/sanchan.o2</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/soundbar__hanaichi</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/za.okinawa</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/essence_taishou</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bar_cococolor_taisho</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/fuku__nchu</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/tms_diner_osaka</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/pizzerialegare</t>
-  </si>
-  <si>
-    <t>003.jpg</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>005.jpg</t>
-  </si>
-  <si>
-    <t>006.jpg</t>
-  </si>
-  <si>
-    <t>007.jpg</t>
-  </si>
-  <si>
-    <t>008.jpg</t>
-  </si>
-  <si>
-    <t>009.jpg</t>
-  </si>
-  <si>
-    <t>010.jpg</t>
-  </si>
-  <si>
-    <t>011.jpg</t>
-  </si>
-  <si>
-    <t>012.jpg</t>
-  </si>
-  <si>
-    <t>013.jpg</t>
-  </si>
-  <si>
-    <t>014.jpg</t>
-  </si>
-  <si>
-    <t>015.jpg</t>
-  </si>
-  <si>
-    <t>016.jpg</t>
-  </si>
-  <si>
-    <t>017.jpg</t>
-  </si>
-  <si>
-    <t>018.jpg</t>
-  </si>
-  <si>
-    <t>019.jpg</t>
-  </si>
-  <si>
-    <t>020.jpg</t>
-  </si>
-  <si>
-    <t>021.jpg</t>
-  </si>
-  <si>
-    <t>022.jpg</t>
-  </si>
-  <si>
-    <t>023.jpg</t>
-  </si>
-  <si>
-    <t>024.jpg</t>
-  </si>
-  <si>
-    <t>025.jpg</t>
-  </si>
-  <si>
-    <t>026.jpg</t>
-  </si>
-  <si>
-    <t>027.jpg</t>
-  </si>
-  <si>
-    <t>028.jpg</t>
-  </si>
-  <si>
-    <t>029.jpg</t>
-  </si>
-  <si>
-    <t>030.jpg</t>
-  </si>
-  <si>
-    <t>031.jpg</t>
-  </si>
-  <si>
-    <t>032.jpg</t>
-  </si>
-  <si>
-    <t>033.jpg</t>
-  </si>
-  <si>
-    <t>004.jpg</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>logo</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>001.png</t>
-  </si>
-  <si>
-    <t>002.png</t>
-  </si>
-  <si>
-    <t>003.png</t>
-  </si>
-  <si>
-    <t>004.png</t>
-  </si>
-  <si>
-    <t>005.png</t>
-  </si>
-  <si>
-    <t>006.png</t>
-  </si>
-  <si>
-    <t>007.png</t>
-  </si>
-  <si>
-    <t>008.png</t>
-  </si>
-  <si>
-    <t>009.png</t>
-  </si>
-  <si>
-    <t>010.png</t>
-  </si>
-  <si>
-    <t>011.png</t>
-  </si>
-  <si>
-    <t>012.png</t>
-  </si>
-  <si>
-    <t>013.png</t>
-  </si>
-  <si>
-    <t>014.png</t>
-  </si>
-  <si>
-    <t>015.png</t>
-  </si>
-  <si>
-    <t>016.png</t>
-  </si>
-  <si>
-    <t>017.png</t>
-  </si>
-  <si>
-    <t>018.png</t>
-  </si>
-  <si>
-    <t>019.png</t>
-  </si>
-  <si>
-    <t>020.png</t>
-  </si>
-  <si>
-    <t>021.png</t>
-  </si>
-  <si>
-    <t>022.png</t>
-  </si>
-  <si>
-    <t>023.png</t>
-  </si>
-  <si>
-    <t>024.png</t>
-  </si>
-  <si>
-    <t>025.png</t>
-  </si>
-  <si>
-    <t>026.png</t>
-  </si>
-  <si>
-    <t>027.png</t>
-  </si>
-  <si>
-    <t>028.png</t>
-  </si>
-  <si>
-    <t>029.png</t>
-  </si>
-  <si>
-    <t>030.png</t>
-  </si>
-  <si>
-    <t>031.png</t>
-  </si>
-  <si>
-    <t>032.png</t>
-  </si>
-  <si>
-    <t>033.png</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/LvrTR4thHgoGpoRc7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/9DHWbdXcG6VwQRg17</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/wSUzPpSDHh3tzyap6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/PB2QxJm3seTe8PFH6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Prnu5oBX6hyQzpft6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/95uXqnFcfkMM8Jwo8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/NL1uEH8kq3MhMEzdA</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rc5NfzqfDAM7pevWA</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/DXhUb1vmR7aNUMMT8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/9Wt44gRpXPDoTt1q9</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Barカセット</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/e85zQpDRWme5xsyr6</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/qM8P7SU6UqcARZm29</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>呑笑戎屋</t>
+    <rPh sb="2" eb="3">
+      <t>ヤス</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1914,7 +2036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1939,8 +2061,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2248,9 +2368,11 @@
   <cols>
     <col min="1" max="1" width="9.5" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="10.5" style="8" customWidth="1"/>
-    <col min="19" max="19" width="10.5" style="12" customWidth="1"/>
-    <col min="20" max="20" width="10.5" style="8" customWidth="1"/>
+    <col min="3" max="5" width="10.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="22.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="20" width="10.5" style="8" customWidth="1"/>
     <col min="21" max="21" width="44.5" style="8" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="39.25" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.625" style="8" bestFit="1" customWidth="1"/>
@@ -2328,7 +2450,7 @@
         <v>23</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2345,22 +2467,19 @@
         <v>28</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="I2" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>39</v>
+        <v>800</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>34</v>
@@ -2386,7 +2505,7 @@
       <c r="R2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="8" t="s">
         <v>41</v>
       </c>
       <c r="T2" s="8" t="s">
@@ -2402,7 +2521,7 @@
         <v>45</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2419,13 +2538,19 @@
         <v>268</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>282</v>
+        <v>448</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1000</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>34</v>
@@ -2433,17 +2558,17 @@
       <c r="L3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U3" s="13" t="s">
-        <v>416</v>
+      <c r="U3" s="8" t="s">
+        <v>413</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2460,13 +2585,19 @@
         <v>273</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>283</v>
+        <v>449</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1000</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>34</v>
@@ -2474,17 +2605,17 @@
       <c r="L4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U4" s="13" t="s">
-        <v>417</v>
+      <c r="U4" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="X4" s="11" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2501,13 +2632,19 @@
         <v>275</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>284</v>
+        <v>450</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1000</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>34</v>
@@ -2515,17 +2652,17 @@
       <c r="L5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U5" s="13" t="s">
-        <v>418</v>
+      <c r="U5" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2542,13 +2679,19 @@
         <v>269</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>285</v>
+        <v>451</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1000</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>34</v>
@@ -2556,17 +2699,17 @@
       <c r="L6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U6" s="13" t="s">
-        <v>419</v>
+      <c r="U6" s="8" t="s">
+        <v>416</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2583,13 +2726,19 @@
         <v>270</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>317</v>
+        <v>482</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>188</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>286</v>
+        <v>452</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1000</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>34</v>
@@ -2597,17 +2746,17 @@
       <c r="L7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U7" s="13" t="s">
-        <v>420</v>
+      <c r="U7" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2624,13 +2773,19 @@
         <v>271</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>190</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>287</v>
+        <v>453</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>34</v>
@@ -2638,17 +2793,17 @@
       <c r="L8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U8" s="13" t="s">
-        <v>421</v>
+      <c r="U8" s="8" t="s">
+        <v>418</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2665,13 +2820,19 @@
         <v>271</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>288</v>
+        <v>454</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1000</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>34</v>
@@ -2679,17 +2840,17 @@
       <c r="L9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U9" s="13" t="s">
-        <v>435</v>
+      <c r="U9" s="8" t="s">
+        <v>432</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2706,13 +2867,19 @@
         <v>276</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>194</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>289</v>
+        <v>455</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1000</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>34</v>
@@ -2720,17 +2887,17 @@
       <c r="L10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U10" s="13" t="s">
-        <v>436</v>
+      <c r="U10" s="8" t="s">
+        <v>433</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2747,13 +2914,19 @@
         <v>274</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>196</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>290</v>
+        <v>456</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I11" s="8">
+        <v>800</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>34</v>
@@ -2761,17 +2934,17 @@
       <c r="L11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U11" s="13" t="s">
-        <v>441</v>
+      <c r="U11" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="V11" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -2788,13 +2961,19 @@
         <v>275</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>291</v>
+        <v>457</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1000</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>34</v>
@@ -2802,17 +2981,17 @@
       <c r="L12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U12" s="13" t="s">
-        <v>434</v>
+      <c r="U12" s="8" t="s">
+        <v>431</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -2829,13 +3008,19 @@
         <v>274</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="F13" s="8">
-        <v>120</v>
+        <v>481</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>292</v>
+        <v>458</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1000</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>34</v>
@@ -2843,17 +3028,17 @@
       <c r="L13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U13" s="13" t="s">
-        <v>428</v>
+      <c r="U13" s="8" t="s">
+        <v>425</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2870,13 +3055,19 @@
         <v>274</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>201</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>293</v>
+        <v>459</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I14" s="8">
+        <v>800</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>34</v>
@@ -2884,17 +3075,17 @@
       <c r="L14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U14" s="13" t="s">
-        <v>422</v>
+      <c r="U14" s="8" t="s">
+        <v>419</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2911,13 +3102,19 @@
         <v>276</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>203</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>294</v>
+        <v>460</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1000</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>34</v>
@@ -2925,17 +3122,17 @@
       <c r="L15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U15" s="13" t="s">
-        <v>429</v>
+      <c r="U15" s="8" t="s">
+        <v>426</v>
       </c>
       <c r="V15" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -2952,13 +3149,19 @@
         <v>274</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>205</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>295</v>
+        <v>461</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1600</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>34</v>
@@ -2966,17 +3169,17 @@
       <c r="L16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U16" s="13" t="s">
-        <v>444</v>
+      <c r="U16" s="8" t="s">
+        <v>441</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2993,13 +3196,19 @@
         <v>28</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>207</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>296</v>
+        <v>462</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I17" s="8">
+        <v>1000</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>34</v>
@@ -3007,17 +3216,17 @@
       <c r="L17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U17" s="13" t="s">
-        <v>438</v>
+      <c r="U17" s="8" t="s">
+        <v>435</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -3034,13 +3243,19 @@
         <v>271</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>317</v>
+        <v>482</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>209</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>297</v>
+        <v>463</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1000</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>34</v>
@@ -3048,17 +3263,17 @@
       <c r="L18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U18" s="13" t="s">
-        <v>430</v>
+      <c r="U18" s="8" t="s">
+        <v>427</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -3075,13 +3290,19 @@
         <v>272</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>211</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>298</v>
+        <v>464</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="I19" s="8">
+        <v>1000</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>34</v>
@@ -3089,17 +3310,17 @@
       <c r="L19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U19" s="13" t="s">
-        <v>439</v>
+      <c r="U19" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="V19" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -3107,7 +3328,7 @@
         <v>253</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>242</v>
@@ -3116,11 +3337,17 @@
         <v>271</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>212</v>
       </c>
+      <c r="G20" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="I20" s="8">
+        <v>300</v>
+      </c>
       <c r="K20" s="8" t="s">
         <v>34</v>
       </c>
@@ -3131,25 +3358,25 @@
         <v>300</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="S20" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="U20" s="13" t="s">
-        <v>442</v>
+        <v>311</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>439</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -3166,13 +3393,19 @@
         <v>273</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>214</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>299</v>
+        <v>466</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="I21" s="8">
+        <v>500</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>34</v>
@@ -3180,17 +3413,17 @@
       <c r="L21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U21" s="13" t="s">
-        <v>440</v>
+      <c r="U21" s="8" t="s">
+        <v>437</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -3207,13 +3440,19 @@
         <v>272</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>216</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>300</v>
+        <v>467</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="I22" s="8">
+        <v>1000</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>34</v>
@@ -3221,17 +3460,17 @@
       <c r="L22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U22" s="13" t="s">
-        <v>437</v>
+      <c r="U22" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -3248,13 +3487,19 @@
         <v>277</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>218</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>301</v>
+        <v>468</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="I23" s="8">
+        <v>1000</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>34</v>
@@ -3262,17 +3507,17 @@
       <c r="L23" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U23" s="13" t="s">
-        <v>431</v>
+      <c r="U23" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -3289,13 +3534,19 @@
         <v>273</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>220</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>302</v>
+        <v>469</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="I24" s="8">
+        <v>1000</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>34</v>
@@ -3303,17 +3554,17 @@
       <c r="L24" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U24" s="13" t="s">
-        <v>433</v>
+      <c r="U24" s="8" t="s">
+        <v>430</v>
       </c>
       <c r="V24" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -3330,13 +3581,19 @@
         <v>274</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>222</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>303</v>
+        <v>470</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1000</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>34</v>
@@ -3345,13 +3602,13 @@
         <v>35</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -3359,7 +3616,7 @@
         <v>259</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>243</v>
@@ -3368,13 +3625,19 @@
         <v>274</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>223</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>304</v>
+        <v>471</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="I26" s="8">
+        <v>800</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>34</v>
@@ -3383,13 +3646,13 @@
         <v>35</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -3406,13 +3669,19 @@
         <v>274</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>225</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>305</v>
+        <v>472</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I27" s="8">
+        <v>1000</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>34</v>
@@ -3420,17 +3689,17 @@
       <c r="L27" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U27" s="13" t="s">
-        <v>432</v>
+      <c r="U27" s="8" t="s">
+        <v>429</v>
       </c>
       <c r="V27" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -3447,13 +3716,19 @@
         <v>278</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>227</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>306</v>
+        <v>473</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="I28" s="8">
+        <v>1000</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>34</v>
@@ -3461,17 +3736,17 @@
       <c r="L28" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U28" s="13" t="s">
-        <v>427</v>
+      <c r="U28" s="8" t="s">
+        <v>424</v>
       </c>
       <c r="V28" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -3488,13 +3763,19 @@
         <v>274</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>229</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>307</v>
+        <v>474</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="I29" s="8">
+        <v>1000</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>34</v>
@@ -3502,17 +3783,17 @@
       <c r="L29" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U29" s="13" t="s">
-        <v>424</v>
+      <c r="U29" s="8" t="s">
+        <v>421</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -3529,13 +3810,19 @@
         <v>274</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>231</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>308</v>
+        <v>475</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="I30" s="8">
+        <v>1000</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>34</v>
@@ -3543,17 +3830,17 @@
       <c r="L30" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U30" s="13" t="s">
-        <v>426</v>
+      <c r="U30" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="V30" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -3570,13 +3857,19 @@
         <v>271</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>233</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>309</v>
+        <v>476</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="I31" s="8">
+        <v>1000</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>34</v>
@@ -3584,17 +3877,17 @@
       <c r="L31" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U31" s="13" t="s">
-        <v>425</v>
+      <c r="U31" s="8" t="s">
+        <v>422</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -3611,13 +3904,19 @@
         <v>274</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>235</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>310</v>
+        <v>477</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="I32" s="8">
+        <v>1000</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>34</v>
@@ -3625,17 +3924,17 @@
       <c r="L32" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U32" s="13" t="s">
-        <v>423</v>
+      <c r="U32" s="8" t="s">
+        <v>420</v>
       </c>
       <c r="V32" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -3652,13 +3951,19 @@
         <v>279</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>281</v>
+        <v>481</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>237</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>311</v>
+        <v>478</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I33" s="8">
+        <v>1000</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>34</v>
@@ -3666,17 +3971,17 @@
       <c r="L33" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U33" s="13" t="s">
-        <v>446</v>
+      <c r="U33" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="V33" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3693,13 +3998,19 @@
         <v>279</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>239</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>312</v>
+        <v>479</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="I34" s="8">
+        <v>800</v>
       </c>
       <c r="K34" s="8" t="s">
         <v>34</v>
@@ -3707,17 +4018,17 @@
       <c r="L34" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U34" s="13" t="s">
-        <v>445</v>
+      <c r="U34" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="V34" s="8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\yoidore-quest2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8D8FAF-E250-4EBA-92D3-AC4122A41423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B69F6-3D75-43A6-8274-7D78DABEB10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7230" yWindow="2550" windowWidth="21570" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="店舗一覧" sheetId="1" r:id="rId1"/>
@@ -624,9 +624,6 @@
     <t>ジビエ・肉料理</t>
   </si>
   <si>
-    <t>CHWEETS</t>
-  </si>
-  <si>
     <t>クレープ酒場・夜カフェ</t>
     <rPh sb="4" eb="6">
       <t>サカバ</t>
@@ -1929,6 +1926,13 @@
     <t>ひと休み</t>
     <rPh sb="2" eb="3">
       <t>ヤス</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CHWEETS　キイロのお店</t>
+    <rPh sb="13" eb="14">
+      <t>ミセ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2450,7 +2454,7 @@
         <v>23</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2461,19 +2465,19 @@
         <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>31</v>
@@ -2521,7 +2525,7 @@
         <v>45</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2532,22 +2536,22 @@
         <v>179</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I3" s="8">
         <v>1000</v>
@@ -2559,16 +2563,16 @@
         <v>35</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2579,22 +2583,22 @@
         <v>181</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I4" s="8">
         <v>1000</v>
@@ -2606,16 +2610,16 @@
         <v>35</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="X4" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2626,22 +2630,22 @@
         <v>183</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I5" s="8">
         <v>1000</v>
@@ -2653,16 +2657,16 @@
         <v>35</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2673,22 +2677,22 @@
         <v>185</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I6" s="8">
         <v>1000</v>
@@ -2700,16 +2704,16 @@
         <v>35</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2717,25 +2721,25 @@
         <v>111</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>188</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I7" s="8">
         <v>1000</v>
@@ -2747,16 +2751,16 @@
         <v>35</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2764,28 +2768,28 @@
         <v>124</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="G8" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>34</v>
@@ -2794,16 +2798,16 @@
         <v>35</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2811,25 +2815,25 @@
         <v>140</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>192</v>
-      </c>
       <c r="G9" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I9" s="8">
         <v>1000</v>
@@ -2841,16 +2845,16 @@
         <v>35</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2858,25 +2862,25 @@
         <v>150</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>194</v>
-      </c>
       <c r="G10" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I10" s="8">
         <v>1000</v>
@@ -2888,16 +2892,16 @@
         <v>35</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2905,25 +2909,25 @@
         <v>162</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="G11" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I11" s="8">
         <v>800</v>
@@ -2935,42 +2939,42 @@
         <v>35</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="V11" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>198</v>
-      </c>
       <c r="G12" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I12" s="8">
         <v>1000</v>
@@ -2982,42 +2986,42 @@
         <v>35</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I13" s="8">
         <v>1000</v>
@@ -3029,42 +3033,42 @@
         <v>35</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="G14" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I14" s="8">
         <v>800</v>
@@ -3076,42 +3080,42 @@
         <v>35</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I15" s="8">
         <v>1000</v>
@@ -3123,42 +3127,42 @@
         <v>35</v>
       </c>
       <c r="U15" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="V15" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>205</v>
-      </c>
       <c r="G16" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I16" s="8">
         <v>1600</v>
@@ -3170,42 +3174,42 @@
         <v>35</v>
       </c>
       <c r="U16" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I17" s="8">
         <v>1000</v>
@@ -3217,42 +3221,42 @@
         <v>35</v>
       </c>
       <c r="U17" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>209</v>
-      </c>
       <c r="G18" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I18" s="8">
         <v>1000</v>
@@ -3264,42 +3268,42 @@
         <v>35</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>211</v>
-      </c>
       <c r="G19" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I19" s="8">
         <v>1000</v>
@@ -3311,39 +3315,39 @@
         <v>35</v>
       </c>
       <c r="U19" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="V19" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I20" s="8">
         <v>300</v>
@@ -3358,51 +3362,51 @@
         <v>300</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R20" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="S20" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="S20" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="U20" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>214</v>
-      </c>
       <c r="G21" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I21" s="8">
         <v>500</v>
@@ -3414,42 +3418,42 @@
         <v>35</v>
       </c>
       <c r="U21" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>216</v>
-      </c>
       <c r="G22" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I22" s="8">
         <v>1000</v>
@@ -3461,42 +3465,42 @@
         <v>35</v>
       </c>
       <c r="U22" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>218</v>
-      </c>
       <c r="G23" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I23" s="8">
         <v>1000</v>
@@ -3508,42 +3512,42 @@
         <v>35</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>220</v>
-      </c>
       <c r="G24" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I24" s="8">
         <v>1000</v>
@@ -3555,42 +3559,42 @@
         <v>35</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="V24" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>222</v>
-      </c>
       <c r="G25" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I25" s="8">
         <v>1000</v>
@@ -3602,39 +3606,39 @@
         <v>35</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I26" s="8">
         <v>800</v>
@@ -3646,39 +3650,39 @@
         <v>35</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>225</v>
-      </c>
       <c r="G27" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I27" s="8">
         <v>1000</v>
@@ -3690,42 +3694,42 @@
         <v>35</v>
       </c>
       <c r="U27" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="V27" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>227</v>
-      </c>
       <c r="G28" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I28" s="8">
         <v>1000</v>
@@ -3737,42 +3741,42 @@
         <v>35</v>
       </c>
       <c r="U28" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="V28" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>229</v>
-      </c>
       <c r="G29" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I29" s="8">
         <v>1000</v>
@@ -3784,42 +3788,42 @@
         <v>35</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>231</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I30" s="8">
         <v>1000</v>
@@ -3831,42 +3835,42 @@
         <v>35</v>
       </c>
       <c r="U30" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="V30" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>233</v>
-      </c>
       <c r="G31" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I31" s="8">
         <v>1000</v>
@@ -3878,42 +3882,42 @@
         <v>35</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B32" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>235</v>
-      </c>
       <c r="G32" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I32" s="8">
         <v>1000</v>
@@ -3925,42 +3929,42 @@
         <v>35</v>
       </c>
       <c r="U32" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="V32" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>237</v>
-      </c>
       <c r="G33" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I33" s="8">
         <v>1000</v>
@@ -3972,42 +3976,42 @@
         <v>35</v>
       </c>
       <c r="U33" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="V33" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B34" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>239</v>
-      </c>
       <c r="G34" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I34" s="8">
         <v>800</v>
@@ -4019,16 +4023,16 @@
         <v>35</v>
       </c>
       <c r="U34" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="V34" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B69F6-3D75-43A6-8274-7D78DABEB10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EA67DA-1C8A-4F31-87E3-69CD27F0B2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7230" yWindow="2550" windowWidth="21570" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="店舗一覧" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="483">
   <si>
     <t>ID</t>
   </si>
@@ -1357,17 +1357,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>成功：会心の1杯サービス、失敗：大魔王のショット(ちょっと)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>不要</t>
-    <rPh sb="0" eb="2">
-      <t>フヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>遊べる・エンタメ</t>
   </si>
   <si>
@@ -1870,9 +1859,6 @@
     <t>創作串焼き三本セット</t>
   </si>
   <si>
-    <t>80's駄菓子バーセット</t>
-  </si>
-  <si>
     <t>昼飲みホルモンおつまみセット</t>
   </si>
   <si>
@@ -1933,6 +1919,25 @@
     <t>CHWEETS　キイロのお店</t>
     <rPh sb="13" eb="14">
       <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成功：会心の1杯サービス
+失敗：大魔王のショット(ちょっと)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クエスト名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クエスト内容</t>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2059,12 +2064,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2368,7 +2379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.5" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="8" bestFit="1" customWidth="1"/>
@@ -2436,10 +2447,10 @@
         <v>17</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>19</v>
+        <v>482</v>
       </c>
       <c r="T1" s="6" t="s">
         <v>20</v>
@@ -2454,30 +2465,30 @@
         <v>23</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>31</v>
@@ -2521,34 +2532,34 @@
       <c r="V2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="11" t="s">
-        <v>379</v>
+      <c r="X2" s="9" t="s">
+        <v>377</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>267</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>279</v>
@@ -2563,39 +2574,39 @@
         <v>35</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>380</v>
+        <v>313</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>272</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>182</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>280</v>
@@ -2610,39 +2621,39 @@
         <v>35</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="X4" s="11" t="s">
-        <v>381</v>
+        <v>314</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>379</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>274</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>184</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>281</v>
@@ -2657,39 +2668,39 @@
         <v>35</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="X5" s="11" t="s">
-        <v>382</v>
+        <v>315</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>268</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>282</v>
@@ -2704,39 +2715,39 @@
         <v>35</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="W6" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="X6" s="11" t="s">
-        <v>383</v>
+        <v>316</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>381</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>111</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="C7" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>269</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>187</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>283</v>
@@ -2751,45 +2762,45 @@
         <v>35</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="W7" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="X7" s="11" t="s">
-        <v>384</v>
+        <v>317</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>382</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>124</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>270</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>189</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>284</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>34</v>
@@ -2798,39 +2809,39 @@
         <v>35</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="W8" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="X8" s="11" t="s">
-        <v>385</v>
+        <v>318</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>140</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>270</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>191</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>285</v>
@@ -2845,39 +2856,39 @@
         <v>35</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="W9" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="X9" s="11" t="s">
-        <v>386</v>
+        <v>319</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>150</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>275</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>193</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>286</v>
@@ -2892,39 +2903,39 @@
         <v>35</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>387</v>
+        <v>320</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>385</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>195</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>287</v>
@@ -2939,39 +2950,39 @@
         <v>35</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="V11" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="W11" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="X11" s="11" t="s">
-        <v>388</v>
+        <v>321</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>386</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>244</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>274</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>197</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>288</v>
@@ -2986,39 +2997,39 @@
         <v>35</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="X12" s="11" t="s">
-        <v>389</v>
+        <v>322</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>387</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>245</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>289</v>
@@ -3033,39 +3044,39 @@
         <v>35</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="X13" s="11" t="s">
-        <v>390</v>
+        <v>323</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>388</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>246</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>200</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>290</v>
@@ -3080,39 +3091,39 @@
         <v>35</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="X14" s="11" t="s">
-        <v>391</v>
+        <v>324</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>389</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>247</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>240</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>275</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>202</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>291</v>
@@ -3127,39 +3138,39 @@
         <v>35</v>
       </c>
       <c r="U15" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="V15" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="W15" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>392</v>
+        <v>325</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>390</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>248</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>204</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>292</v>
@@ -3174,39 +3185,39 @@
         <v>35</v>
       </c>
       <c r="U16" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>393</v>
+        <v>326</v>
+      </c>
+      <c r="W16" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>391</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>249</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>206</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>293</v>
@@ -3221,39 +3232,39 @@
         <v>35</v>
       </c>
       <c r="U17" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>394</v>
+        <v>327</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>392</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
         <v>250</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>270</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>208</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>294</v>
@@ -3268,39 +3279,39 @@
         <v>35</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="W18" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="X18" s="11" t="s">
-        <v>395</v>
+        <v>328</v>
+      </c>
+      <c r="W18" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>393</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
         <v>251</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>271</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>210</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>295</v>
@@ -3315,43 +3326,37 @@
         <v>35</v>
       </c>
       <c r="U19" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="V19" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="W19" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="X19" s="11" t="s">
-        <v>396</v>
+        <v>329</v>
+      </c>
+      <c r="W19" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="X19" s="9" t="s">
+        <v>394</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="71.25" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
         <v>252</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="C20" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>270</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="I20" s="8">
-        <v>300</v>
-      </c>
       <c r="K20" s="8" t="s">
         <v>34</v>
       </c>
@@ -3362,48 +3367,48 @@
         <v>300</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>312</v>
+        <v>177</v>
       </c>
       <c r="R20" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="S20" s="8" t="s">
-        <v>311</v>
+      <c r="S20" s="11" t="s">
+        <v>480</v>
       </c>
       <c r="U20" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="X20" s="11" t="s">
-        <v>397</v>
+        <v>330</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>395</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
         <v>253</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>272</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>213</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>296</v>
@@ -3418,39 +3423,39 @@
         <v>35</v>
       </c>
       <c r="U21" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="W21" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>398</v>
+        <v>331</v>
+      </c>
+      <c r="W21" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>396</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>254</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>271</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>215</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>297</v>
@@ -3465,39 +3470,39 @@
         <v>35</v>
       </c>
       <c r="U22" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>399</v>
+        <v>332</v>
+      </c>
+      <c r="W22" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>397</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
         <v>255</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>276</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>217</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>298</v>
@@ -3512,39 +3517,39 @@
         <v>35</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="W23" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="X23" s="11" t="s">
-        <v>400</v>
+        <v>333</v>
+      </c>
+      <c r="W23" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="X23" s="9" t="s">
+        <v>398</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
         <v>256</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>272</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>219</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>299</v>
@@ -3559,39 +3564,39 @@
         <v>35</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="V24" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>401</v>
+        <v>334</v>
+      </c>
+      <c r="W24" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="X24" s="9" t="s">
+        <v>399</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
         <v>257</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>221</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>300</v>
@@ -3606,36 +3611,36 @@
         <v>35</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="W25" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>402</v>
+        <v>335</v>
+      </c>
+      <c r="W25" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>400</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
         <v>258</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="C26" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>222</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>301</v>
@@ -3650,36 +3655,36 @@
         <v>35</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="W26" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>403</v>
+        <v>336</v>
+      </c>
+      <c r="W26" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="X26" s="9" t="s">
+        <v>401</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
         <v>259</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>224</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>302</v>
@@ -3694,39 +3699,39 @@
         <v>35</v>
       </c>
       <c r="U27" s="8" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="V27" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="W27" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="X27" s="11" t="s">
-        <v>404</v>
+        <v>337</v>
+      </c>
+      <c r="W27" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="X27" s="9" t="s">
+        <v>402</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>260</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>277</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>226</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>303</v>
@@ -3741,39 +3746,39 @@
         <v>35</v>
       </c>
       <c r="U28" s="8" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="V28" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="W28" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="X28" s="11" t="s">
-        <v>405</v>
+        <v>338</v>
+      </c>
+      <c r="W28" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>261</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>228</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>304</v>
@@ -3788,39 +3793,39 @@
         <v>35</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="W29" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="X29" s="11" t="s">
-        <v>406</v>
+        <v>339</v>
+      </c>
+      <c r="W29" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>262</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>240</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>230</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>305</v>
@@ -3835,39 +3840,39 @@
         <v>35</v>
       </c>
       <c r="U30" s="8" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="V30" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="W30" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="X30" s="11" t="s">
-        <v>407</v>
+        <v>340</v>
+      </c>
+      <c r="W30" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>263</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>270</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>232</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>306</v>
@@ -3882,39 +3887,39 @@
         <v>35</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="W31" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="X31" s="11" t="s">
-        <v>408</v>
+        <v>341</v>
+      </c>
+      <c r="W31" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="X31" s="9" t="s">
+        <v>406</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>264</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>273</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>234</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>307</v>
@@ -3929,39 +3934,39 @@
         <v>35</v>
       </c>
       <c r="U32" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="V32" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="W32" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="X32" s="11" t="s">
-        <v>409</v>
+        <v>342</v>
+      </c>
+      <c r="W32" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="X32" s="9" t="s">
+        <v>407</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>265</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>241</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>278</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>236</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>308</v>
@@ -3976,19 +3981,19 @@
         <v>35</v>
       </c>
       <c r="U33" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="V33" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="W33" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="X33" s="11" t="s">
-        <v>410</v>
+        <v>343</v>
+      </c>
+      <c r="W33" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="X33" s="9" t="s">
+        <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>266</v>
       </c>
@@ -4002,13 +4007,13 @@
         <v>278</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>238</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>309</v>
@@ -4023,16 +4028,16 @@
         <v>35</v>
       </c>
       <c r="U34" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="V34" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="W34" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="X34" s="11" t="s">
-        <v>411</v>
+        <v>344</v>
+      </c>
+      <c r="W34" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="X34" s="9" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
